--- a/Aeterna dokumentációk/CARDDATABASE.xlsx
+++ b/Aeterna dokumentációk/CARDDATABASE.xlsx
@@ -7,24 +7,25 @@
     <sheet state="visible" name="CHANGELOG" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="EXPORT_MANIFEST" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="SETS" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="CARDS" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="CARD_LOCALIZATION" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="CARD_PRINTINGS" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="CARD_KEYWORDS" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="CARD_TRAITS" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="ABILITIES" sheetId="10" r:id="rId14"/>
-    <sheet state="visible" name="ABILITY_TRIGGERS" sheetId="11" r:id="rId15"/>
-    <sheet state="visible" name="ABILITY_CONDITIONS" sheetId="12" r:id="rId16"/>
-    <sheet state="visible" name="ABILITY_TARGETS" sheetId="13" r:id="rId17"/>
-    <sheet state="visible" name="ABILITY_COSTS" sheetId="14" r:id="rId18"/>
-    <sheet state="visible" name="ABILITY_EFFECTS" sheetId="15" r:id="rId19"/>
-    <sheet state="visible" name="ABILITY_DURATIONS" sheetId="16" r:id="rId20"/>
-    <sheet state="visible" name="ABILITY_USAGE_LIMITS" sheetId="17" r:id="rId21"/>
-    <sheet state="visible" name="ABILITY_CHOICES" sheetId="18" r:id="rId22"/>
-    <sheet state="visible" name="ABILITY_CHOICE_OPTIONS" sheetId="19" r:id="rId23"/>
-    <sheet state="visible" name="ABILITY_EXPRESSIONS" sheetId="20" r:id="rId24"/>
-    <sheet state="visible" name="EFFECT_TAGS" sheetId="21" r:id="rId25"/>
-    <sheet state="visible" name="CARD_RELATIONS" sheetId="22" r:id="rId26"/>
+    <sheet state="visible" name="SET_LOCALIZATION" sheetId="5" r:id="rId9"/>
+    <sheet state="visible" name="CARDS" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="CARD_LOCALIZATION" sheetId="7" r:id="rId11"/>
+    <sheet state="visible" name="CARD_PRINTINGS" sheetId="8" r:id="rId12"/>
+    <sheet state="visible" name="CARD_KEYWORDS" sheetId="9" r:id="rId13"/>
+    <sheet state="visible" name="CARD_TRAITS" sheetId="10" r:id="rId14"/>
+    <sheet state="visible" name="ABILITIES" sheetId="11" r:id="rId15"/>
+    <sheet state="visible" name="ABILITY_TRIGGERS" sheetId="12" r:id="rId16"/>
+    <sheet state="visible" name="ABILITY_CONDITIONS" sheetId="13" r:id="rId17"/>
+    <sheet state="visible" name="ABILITY_TARGETS" sheetId="14" r:id="rId18"/>
+    <sheet state="visible" name="ABILITY_COSTS" sheetId="15" r:id="rId19"/>
+    <sheet state="visible" name="ABILITY_EFFECTS" sheetId="16" r:id="rId20"/>
+    <sheet state="visible" name="ABILITY_DURATIONS" sheetId="17" r:id="rId21"/>
+    <sheet state="visible" name="ABILITY_USAGE_LIMITS" sheetId="18" r:id="rId22"/>
+    <sheet state="visible" name="ABILITY_CHOICES" sheetId="19" r:id="rId23"/>
+    <sheet state="visible" name="ABILITY_CHOICE_OPTIONS" sheetId="20" r:id="rId24"/>
+    <sheet state="visible" name="ABILITY_EXPRESSIONS" sheetId="21" r:id="rId25"/>
+    <sheet state="visible" name="EFFECT_TAGS" sheetId="22" r:id="rId26"/>
+    <sheet state="visible" name="CARD_RELATIONS" sheetId="23" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -32,95 +33,98 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="157">
+  <si>
+    <t>change_id</t>
+  </si>
+  <si>
+    <t>set_id</t>
+  </si>
   <si>
     <t>key</t>
   </si>
   <si>
+    <t>table_id</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>set_code</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>change_date</t>
+  </si>
+  <si>
+    <t>export_enabled</t>
+  </si>
+  <si>
+    <t>rules_layer</t>
+  </si>
+  <si>
+    <t>value_type</t>
+  </si>
+  <si>
     <t>sheet_name</t>
   </si>
   <si>
-    <t>change_id</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>export_enabled</t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>value_type</t>
+    <t>release_order</t>
   </si>
   <si>
     <t>output_name</t>
   </si>
   <si>
-    <t>change_date</t>
-  </si>
-  <si>
-    <t>set_id</t>
-  </si>
-  <si>
     <t>description</t>
   </si>
   <si>
+    <t>record_id</t>
+  </si>
+  <si>
+    <t>release_date</t>
+  </si>
+  <si>
     <t>output_format</t>
   </si>
   <si>
-    <t>record_type</t>
-  </si>
-  <si>
-    <t>record_id</t>
-  </si>
-  <si>
-    <t>set_code</t>
-  </si>
-  <si>
-    <t>schema_version</t>
-  </si>
-  <si>
     <t>change_type</t>
   </si>
   <si>
-    <t>name_key</t>
-  </si>
-  <si>
-    <t>primary_key</t>
+    <t>status</t>
+  </si>
+  <si>
+    <t>load_order</t>
   </si>
   <si>
     <t>summary</t>
   </si>
   <si>
-    <t>load_order</t>
-  </si>
-  <si>
-    <t>rules_layer</t>
+    <t>source_id</t>
+  </si>
+  <si>
+    <t>notes</t>
   </si>
   <si>
     <t>decision_id</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>release_order</t>
-  </si>
-  <si>
-    <t>release_date</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>source_id</t>
-  </si>
-  <si>
     <t>source_ref</t>
   </si>
   <si>
+    <t>set_localization_id</t>
+  </si>
+  <si>
+    <t>language</t>
+  </si>
+  <si>
+    <t>set_name</t>
+  </si>
+  <si>
+    <t>short_name</t>
+  </si>
+  <si>
     <t>card_id</t>
   </si>
   <si>
@@ -154,24 +158,18 @@
     <t>is_unique</t>
   </si>
   <si>
+    <t>card_localization_id</t>
+  </si>
+  <si>
     <t>is_token_definition</t>
   </si>
   <si>
-    <t>origin_set_id</t>
-  </si>
-  <si>
-    <t>default_printing_id</t>
+    <t>introduced_in_set_id</t>
   </si>
   <si>
     <t>engine_support_status</t>
   </si>
   <si>
-    <t>card_localization_id</t>
-  </si>
-  <si>
-    <t>language</t>
-  </si>
-  <si>
     <t>card_name</t>
   </si>
   <si>
@@ -226,10 +224,7 @@
     <t>card_trait_id</t>
   </si>
   <si>
-    <t>trait_group_id</t>
-  </si>
-  <si>
-    <t>trait_value_id</t>
+    <t>trait_registry_value_id</t>
   </si>
   <si>
     <t>is_primary</t>
@@ -244,6 +239,9 @@
     <t>ability_kind_id</t>
   </si>
   <si>
+    <t>trigger_id</t>
+  </si>
+  <si>
     <t>resolution_requirement_id</t>
   </si>
   <si>
@@ -253,13 +251,37 @@
     <t>implementation_mode</t>
   </si>
   <si>
+    <t>event_type_id</t>
+  </si>
+  <si>
     <t>module_key</t>
   </si>
   <si>
+    <t>event_stage_id</t>
+  </si>
+  <si>
     <t>parent_ability_id</t>
   </si>
   <si>
-    <t>trigger_id</t>
+    <t>subject_reference_type_id</t>
+  </si>
+  <si>
+    <t>player_reference_type_id</t>
+  </si>
+  <si>
+    <t>phase_id</t>
+  </si>
+  <si>
+    <t>from_zone_id</t>
+  </si>
+  <si>
+    <t>to_zone_id</t>
+  </si>
+  <si>
+    <t>filter_condition_id</t>
+  </si>
+  <si>
+    <t>timing_window_id</t>
   </si>
   <si>
     <t>condition_id</t>
@@ -268,231 +290,192 @@
     <t>parent_condition_id</t>
   </si>
   <si>
-    <t>event_type_id</t>
-  </si>
-  <si>
-    <t>event_stage_id</t>
-  </si>
-  <si>
-    <t>scope_id</t>
-  </si>
-  <si>
-    <t>subject_reference_type_id</t>
+    <t>condition_kind_id</t>
   </si>
   <si>
     <t>logical_operator_id</t>
   </si>
   <si>
-    <t>player_reference_type_id</t>
-  </si>
-  <si>
     <t>negated</t>
   </si>
   <si>
-    <t>phase_id</t>
-  </si>
-  <si>
-    <t>left_reference_type_id</t>
-  </si>
-  <si>
-    <t>from_zone_id</t>
+    <t>left_expression_id</t>
+  </si>
+  <si>
+    <t>comparison_operator_id</t>
+  </si>
+  <si>
+    <t>right_expression_id</t>
+  </si>
+  <si>
+    <t>target_id</t>
+  </si>
+  <si>
+    <t>target_role_id</t>
+  </si>
+  <si>
+    <t>target_primitive_id</t>
+  </si>
+  <si>
+    <t>reference_type_id</t>
+  </si>
+  <si>
+    <t>object_type_id</t>
+  </si>
+  <si>
+    <t>zone_id</t>
+  </si>
+  <si>
+    <t>board_position_id</t>
+  </si>
+  <si>
+    <t>selection_method_id</t>
+  </si>
+  <si>
+    <t>minimum_targets</t>
+  </si>
+  <si>
+    <t>maximum_targets</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>cost_id</t>
+  </si>
+  <si>
+    <t>cost_component_type_id</t>
+  </si>
+  <si>
+    <t>amount_number</t>
+  </si>
+  <si>
+    <t>amount_expression_id</t>
+  </si>
+  <si>
+    <t>source_reference_type_id</t>
+  </si>
+  <si>
+    <t>effect_id</t>
+  </si>
+  <si>
+    <t>additional_cost</t>
+  </si>
+  <si>
+    <t>parent_effect_id</t>
+  </si>
+  <si>
+    <t>refundable</t>
+  </si>
+  <si>
+    <t>branch_key</t>
+  </si>
+  <si>
+    <t>effect_action_type_id</t>
+  </si>
+  <si>
+    <t>value_number</t>
+  </si>
+  <si>
+    <t>value_text</t>
+  </si>
+  <si>
+    <t>value_id</t>
+  </si>
+  <si>
+    <t>value_expression_id</t>
   </si>
   <si>
     <t>field_id</t>
   </si>
   <si>
-    <t>to_zone_id</t>
+    <t>destination_position_id</t>
+  </si>
+  <si>
+    <t>modifier_type_id</t>
+  </si>
+  <si>
+    <t>restriction_type_id</t>
+  </si>
+  <si>
+    <t>duration_id</t>
+  </si>
+  <si>
+    <t>duration_policy_id</t>
+  </si>
+  <si>
+    <t>start_event_type_id</t>
+  </si>
+  <si>
+    <t>boundary_player_reference_type_id</t>
+  </si>
+  <si>
+    <t>boundary_phase_id</t>
+  </si>
+  <si>
+    <t>expiration_event_type_id</t>
+  </si>
+  <si>
+    <t>dependency_reference_type_id</t>
+  </si>
+  <si>
+    <t>maximum_applications</t>
+  </si>
+  <si>
+    <t>usage_limit_id</t>
+  </si>
+  <si>
+    <t>usage_limit_policy_id</t>
+  </si>
+  <si>
+    <t>maximum_uses</t>
+  </si>
+  <si>
+    <t>reset_event_type_id</t>
+  </si>
+  <si>
+    <t>tracking_scope_id</t>
+  </si>
+  <si>
+    <t>shared_key</t>
+  </si>
+  <si>
+    <t>choice_id</t>
+  </si>
+  <si>
+    <t>chooser_reference_type_id</t>
+  </si>
+  <si>
+    <t>choice_kind_id</t>
+  </si>
+  <si>
+    <t>minimum_choices</t>
+  </si>
+  <si>
+    <t>maximum_choices</t>
+  </si>
+  <si>
+    <t>choice_option_id</t>
+  </si>
+  <si>
+    <t>label_key</t>
+  </si>
+  <si>
+    <t>expression_id</t>
+  </si>
+  <si>
+    <t>parent_expression_id</t>
+  </si>
+  <si>
+    <t>expression_kind_id</t>
+  </si>
+  <si>
+    <t>operator_id</t>
   </si>
   <si>
     <t>aggregate_type_id</t>
   </si>
   <si>
-    <t>filter_condition_id</t>
-  </si>
-  <si>
-    <t>comparison_operator_id</t>
-  </si>
-  <si>
-    <t>timing_window_id</t>
-  </si>
-  <si>
-    <t>right_value_type</t>
-  </si>
-  <si>
-    <t>right_number</t>
-  </si>
-  <si>
-    <t>right_text</t>
-  </si>
-  <si>
-    <t>right_value_id</t>
-  </si>
-  <si>
-    <t>right_reference_type_id</t>
-  </si>
-  <si>
-    <t>target_id</t>
-  </si>
-  <si>
-    <t>target_role_id</t>
-  </si>
-  <si>
-    <t>target_primitive_id</t>
-  </si>
-  <si>
-    <t>reference_type_id</t>
-  </si>
-  <si>
-    <t>object_type_id</t>
-  </si>
-  <si>
-    <t>zone_id</t>
-  </si>
-  <si>
-    <t>board_position_id</t>
-  </si>
-  <si>
-    <t>selection_method_id</t>
-  </si>
-  <si>
-    <t>minimum_targets</t>
-  </si>
-  <si>
-    <t>maximum_targets</t>
-  </si>
-  <si>
-    <t>optional</t>
-  </si>
-  <si>
-    <t>cost_id</t>
-  </si>
-  <si>
-    <t>cost_component_type_id</t>
-  </si>
-  <si>
-    <t>amount_number</t>
-  </si>
-  <si>
-    <t>amount_expression_id</t>
-  </si>
-  <si>
-    <t>source_reference_type_id</t>
-  </si>
-  <si>
-    <t>additional_cost</t>
-  </si>
-  <si>
-    <t>refundable</t>
-  </si>
-  <si>
-    <t>effect_id</t>
-  </si>
-  <si>
-    <t>parent_effect_id</t>
-  </si>
-  <si>
-    <t>branch_key</t>
-  </si>
-  <si>
-    <t>effect_action_type_id</t>
-  </si>
-  <si>
-    <t>value_number</t>
-  </si>
-  <si>
-    <t>value_text</t>
-  </si>
-  <si>
-    <t>value_id</t>
-  </si>
-  <si>
-    <t>value_expression_id</t>
-  </si>
-  <si>
-    <t>destination_position_id</t>
-  </si>
-  <si>
-    <t>modifier_type_id</t>
-  </si>
-  <si>
-    <t>restriction_type_id</t>
-  </si>
-  <si>
-    <t>duration_id</t>
-  </si>
-  <si>
-    <t>duration_policy_id</t>
-  </si>
-  <si>
-    <t>start_event_type_id</t>
-  </si>
-  <si>
-    <t>boundary_player_reference_type_id</t>
-  </si>
-  <si>
-    <t>boundary_phase_id</t>
-  </si>
-  <si>
-    <t>expiration_event_type_id</t>
-  </si>
-  <si>
-    <t>dependency_reference_type_id</t>
-  </si>
-  <si>
-    <t>maximum_applications</t>
-  </si>
-  <si>
-    <t>usage_limit_id</t>
-  </si>
-  <si>
-    <t>usage_limit_policy_id</t>
-  </si>
-  <si>
-    <t>maximum_uses</t>
-  </si>
-  <si>
-    <t>reset_event_type_id</t>
-  </si>
-  <si>
-    <t>tracking_scope_id</t>
-  </si>
-  <si>
-    <t>shared_key</t>
-  </si>
-  <si>
-    <t>choice_id</t>
-  </si>
-  <si>
-    <t>chooser_reference_type_id</t>
-  </si>
-  <si>
-    <t>choice_kind_id</t>
-  </si>
-  <si>
-    <t>minimum_choices</t>
-  </si>
-  <si>
-    <t>maximum_choices</t>
-  </si>
-  <si>
-    <t>choice_option_id</t>
-  </si>
-  <si>
-    <t>label_key</t>
-  </si>
-  <si>
-    <t>expression_id</t>
-  </si>
-  <si>
-    <t>parent_expression_id</t>
-  </si>
-  <si>
-    <t>expression_kind_id</t>
-  </si>
-  <si>
-    <t>operator_id</t>
-  </si>
-  <si>
     <t>literal_type</t>
   </si>
   <si>
@@ -502,10 +485,10 @@
     <t>literal_text</t>
   </si>
   <si>
+    <t>literal_value_id</t>
+  </si>
+  <si>
     <t>effect_tag_id</t>
-  </si>
-  <si>
-    <t>literal_value_id</t>
   </si>
   <si>
     <t>tag_id</t>
@@ -626,6 +609,10 @@
 </file>
 
 <file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -864,17 +851,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -882,6 +869,50 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="17.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -896,43 +927,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>23</v>
@@ -943,7 +974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -958,49 +989,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>23</v>
@@ -1011,7 +1042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1019,73 +1050,57 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="15.63"/>
+    <col customWidth="1" min="5" max="5" width="13.88"/>
     <col customWidth="1" min="6" max="6" width="15.13"/>
     <col customWidth="1" min="8" max="8" width="17.5"/>
-    <col customWidth="1" min="10" max="10" width="14.88"/>
-    <col customWidth="1" min="11" max="11" width="19.0"/>
+    <col customWidth="1" min="9" max="9" width="19.0"/>
+    <col customWidth="1" min="10" max="10" width="15.5"/>
+    <col customWidth="1" min="11" max="11" width="5.5"/>
     <col customWidth="1" min="12" max="12" width="13.25"/>
     <col customWidth="1" min="16" max="16" width="18.63"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>90</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1094,7 +1109,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1113,61 +1128,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>23</v>
@@ -1178,7 +1193,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1193,49 +1208,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>23</v>
@@ -1246,7 +1261,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1260,86 +1275,150 @@
     <col customWidth="1" min="17" max="17" width="18.0"/>
     <col customWidth="1" min="18" max="18" width="13.25"/>
     <col customWidth="1" min="19" max="19" width="14.63"/>
-    <col customWidth="1" min="23" max="23" width="17.88"/>
+    <col customWidth="1" min="22" max="22" width="17.88"/>
+    <col customWidth="1" min="23" max="23" width="8.25"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
+      <c r="R1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="15.63"/>
+    <col customWidth="1" min="5" max="5" width="27.75"/>
+    <col customWidth="1" min="6" max="6" width="15.75"/>
+    <col customWidth="1" min="7" max="7" width="19.63"/>
+    <col customWidth="1" min="8" max="8" width="24.5"/>
+    <col customWidth="1" min="9" max="9" width="9.88"/>
+    <col customWidth="1" min="10" max="10" width="18.0"/>
+    <col customWidth="1" min="11" max="11" width="5.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>124</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="W1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1348,75 +1427,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="4" max="4" width="14.5"/>
-    <col customWidth="1" min="5" max="5" width="15.63"/>
-    <col customWidth="1" min="6" max="6" width="27.75"/>
-    <col customWidth="1" min="7" max="7" width="15.75"/>
-    <col customWidth="1" min="8" max="8" width="19.63"/>
-    <col customWidth="1" min="9" max="9" width="24.5"/>
-    <col customWidth="1" min="11" max="11" width="18.0"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1430,34 +1441,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>138</v>
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>23</v>
@@ -1468,7 +1479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1482,37 +1493,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>135</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>23</v>
@@ -1523,7 +1534,48 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1535,34 +1587,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>148</v>
+        <v>140</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>23</v>
@@ -1573,48 +1625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1629,52 +1640,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>23</v>
@@ -1685,34 +1696,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>158</v>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>23</v>
@@ -1723,7 +1734,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1736,33 +1747,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1783,28 +1791,60 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>23</v>
@@ -1815,40 +1855,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1" t="s">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="14.63"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>23</v>
@@ -1859,7 +1902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1867,69 +1910,67 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="12" max="12" width="14.88"/>
+    <col customWidth="1" min="13" max="13" width="16.5"/>
     <col customWidth="1" min="14" max="14" width="14.63"/>
     <col customWidth="1" min="17" max="17" width="17.88"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="T1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1938,7 +1979,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -1950,34 +1991,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="H1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>23</v>
@@ -1988,7 +2029,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2002,46 +2043,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="L1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>23</v>
@@ -2052,7 +2093,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -2064,31 +2105,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>23</v>
@@ -2097,48 +2138,4 @@
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <drawing r:id="rId1"/>
-</worksheet>
 </file>
--- a/Aeterna dokumentációk/CARDDATABASE.xlsx
+++ b/Aeterna dokumentációk/CARDDATABASE.xlsx
@@ -33,86 +33,290 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="225">
+  <si>
+    <t>table_id</t>
+  </si>
   <si>
     <t>change_id</t>
   </si>
   <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>export_enabled</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>output_name</t>
+  </si>
+  <si>
     <t>set_id</t>
   </si>
   <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>table_id</t>
-  </si>
-  <si>
-    <t>version</t>
+    <t>change_date</t>
+  </si>
+  <si>
+    <t>output_format</t>
+  </si>
+  <si>
+    <t>value_type</t>
+  </si>
+  <si>
+    <t>load_order</t>
+  </si>
+  <si>
+    <t>sheet_name</t>
+  </si>
+  <si>
+    <t>description</t>
   </si>
   <si>
     <t>set_code</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>change_date</t>
-  </si>
-  <si>
-    <t>export_enabled</t>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>record_id</t>
   </si>
   <si>
     <t>rules_layer</t>
   </si>
   <si>
-    <t>value_type</t>
-  </si>
-  <si>
-    <t>sheet_name</t>
+    <t>workbook_id</t>
+  </si>
+  <si>
+    <t>change_type</t>
   </si>
   <si>
     <t>release_order</t>
   </si>
   <si>
-    <t>output_name</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>record_id</t>
+    <t>aeterna_carddatabase</t>
   </si>
   <si>
     <t>release_date</t>
   </si>
   <si>
-    <t>output_format</t>
-  </si>
-  <si>
-    <t>change_type</t>
+    <t>summary</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>status</t>
   </si>
   <si>
-    <t>load_order</t>
-  </si>
-  <si>
-    <t>summary</t>
+    <t>decision_id</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE.xlsx szerkesztési és auditálási munkafüzet stabil azonosítója. Runtime hivatkozásra nem használható.</t>
   </si>
   <si>
     <t>source_id</t>
   </si>
   <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>decision_id</t>
-  </si>
-  <si>
     <t>source_ref</t>
   </si>
   <si>
+    <t>workbook_role</t>
+  </si>
+  <si>
+    <t>canonical_card_data_editor</t>
+  </si>
+  <si>
+    <t>A canonical kártya-, printing-, lokalizáció-, keyword- és ability-adatok szerkesztési forrása.</t>
+  </si>
+  <si>
+    <t>schema_version</t>
+  </si>
+  <si>
+    <t>0.1.0</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE első normalizált sémaverziója.</t>
+  </si>
+  <si>
+    <t>data_version</t>
+  </si>
+  <si>
+    <t>0.0.0</t>
+  </si>
+  <si>
+    <t>Az adatbetöltés előtti üres bootstrap-adatréteg verziója.</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>A munkafüzet jelenleg séma-előkészítési állapotban van.</t>
+  </si>
+  <si>
+    <t>canonical_language</t>
+  </si>
+  <si>
+    <t>hu-HU</t>
+  </si>
+  <si>
+    <t>language_tag</t>
+  </si>
+  <si>
+    <t>A canonical szerkesztési és természetes szabályszöveg nyelve.</t>
+  </si>
+  <si>
+    <t>export_directory_name</t>
+  </si>
+  <si>
+    <t>CARDDATABASE</t>
+  </si>
+  <si>
+    <t>A munkafüzetből előállított JSON- és JSONL-fájlok alapértelmezett könyvtárneve.</t>
+  </si>
+  <si>
+    <t>export_manifest_file</t>
+  </si>
+  <si>
+    <t>export_manifest.json</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE exportált tábláit és tényleges fájlneveit tartalmazó JSON-manifest.</t>
+  </si>
+  <si>
+    <t>runtime_input_policy</t>
+  </si>
+  <si>
+    <t>json_jsonl_exports_only</t>
+  </si>
+  <si>
+    <t>A program kizárólag a CARDDATABASE munkalapjaiból előállított JSON és JSONL exportfájlokat használhatja.</t>
+  </si>
+  <si>
+    <t>registry_manifest_reference</t>
+  </si>
+  <si>
+    <t>../REGISTRY/export_manifest.json</t>
+  </si>
+  <si>
+    <t>file_reference</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE exportcsomag által használt registry-táblakatalógus JSON-fájlja. Nem XLSX-hivatkozás.</t>
+  </si>
+  <si>
+    <t>registry_meta_reference</t>
+  </si>
+  <si>
+    <t>../REGISTRY/registry.meta.json</t>
+  </si>
+  <si>
+    <t>A szükséges registry-séma- és adatverziók ellenőrzésére használt exportált META.json fájl.</t>
+  </si>
+  <si>
+    <t>minimum_registry_schema_version</t>
+  </si>
+  <si>
+    <t>0.4.0</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE 0.1.0 sémával kompatibilis minimális REGISTRY-sémaverzió.</t>
+  </si>
+  <si>
+    <t>cross_file_reference_policy</t>
+  </si>
+  <si>
+    <t>table_id_via_export_manifests</t>
+  </si>
+  <si>
+    <t>A CARDDATABASE és REGISTRY JSON/JSONL rekordjai közötti kapcsolatokat logical table_id, elsődleges kulcs és a két EXPORT_MANIFEST alapján kell feloldani.</t>
+  </si>
+  <si>
+    <t>legacy_runtime_policy</t>
+  </si>
+  <si>
+    <t>forbidden</t>
+  </si>
+  <si>
+    <t>Legacy vagy aktuális XLSX-fájl közvetlen runtime-betöltése tilos.</t>
+  </si>
+  <si>
+    <t>legacy_migration_policy</t>
+  </si>
+  <si>
+    <t>staging_and_audited_mapping_only</t>
+  </si>
+  <si>
+    <t>Legacy adat kizárólag staging, migrációs megfeleltetés és audit után kerülhet canonical exportba.</t>
+  </si>
+  <si>
+    <t>null_sentinel</t>
+  </si>
+  <si>
+    <t>#NULL</t>
+  </si>
+  <si>
+    <t>A szándékosan nem alkalmazható érték jelölése.</t>
+  </si>
+  <si>
+    <t>tbd_sentinel</t>
+  </si>
+  <si>
+    <t>#TBD</t>
+  </si>
+  <si>
+    <t>A production export előtt kötelezően feloldandó érték jelölése.</t>
+  </si>
+  <si>
+    <t>production_tbd_policy</t>
+  </si>
+  <si>
+    <t>reject</t>
+  </si>
+  <si>
+    <t>A #TBD értéket tartalmazó rekord nem kerülhet production JSON- vagy JSONL-exportba.</t>
+  </si>
+  <si>
+    <t>final_workbook_filename</t>
+  </si>
+  <si>
+    <t>CARDDATABASE.xlsx</t>
+  </si>
+  <si>
+    <t>A szerkesztési munkafüzet végleges fájlneve. A program nem hivatkozik rá.</t>
+  </si>
+  <si>
+    <t>export_namespace</t>
+  </si>
+  <si>
+    <t>carddatabase</t>
+  </si>
+  <si>
+    <t>A munkafüzet exportált fájlneveiben használt stabil kisbetűs névtér.</t>
+  </si>
+  <si>
+    <t>export_filename_policy</t>
+  </si>
+  <si>
+    <t>namespace_dot_sheet_name_lowercase</t>
+  </si>
+  <si>
+    <t>Az exportfájl neve az export_namespace, egy pont, a munkalap kisbetűs neve és a formátum szerinti kiterjesztés: például carddatabase.cards.json.</t>
+  </si>
+  <si>
+    <t>export_filename_case_policy</t>
+  </si>
+  <si>
+    <t>lowercase</t>
+  </si>
+  <si>
+    <t>Minden exportált fájlnév kizárólag kisbetűket, számokat, pontot és aláhúzásjelet használhat a Windows- és Linux-kompatibilitás érdekében.</t>
+  </si>
+  <si>
     <t>set_localization_id</t>
   </si>
   <si>
@@ -131,6 +335,9 @@
     <t>card_type_id</t>
   </si>
   <si>
+    <t>card_localization_id</t>
+  </si>
+  <si>
     <t>realm_id</t>
   </si>
   <si>
@@ -143,12 +350,24 @@
     <t>class_id</t>
   </si>
   <si>
+    <t>card_name</t>
+  </si>
+  <si>
+    <t>rules_text</t>
+  </si>
+  <si>
     <t>magnitude</t>
   </si>
   <si>
+    <t>flavor_text</t>
+  </si>
+  <si>
     <t>aura_cost</t>
   </si>
   <si>
+    <t>search_name</t>
+  </si>
+  <si>
     <t>atk</t>
   </si>
   <si>
@@ -158,33 +377,18 @@
     <t>is_unique</t>
   </si>
   <si>
-    <t>card_localization_id</t>
-  </si>
-  <si>
     <t>is_token_definition</t>
   </si>
   <si>
     <t>introduced_in_set_id</t>
   </si>
   <si>
+    <t>printing_id</t>
+  </si>
+  <si>
     <t>engine_support_status</t>
   </si>
   <si>
-    <t>card_name</t>
-  </si>
-  <si>
-    <t>rules_text</t>
-  </si>
-  <si>
-    <t>flavor_text</t>
-  </si>
-  <si>
-    <t>search_name</t>
-  </si>
-  <si>
-    <t>printing_id</t>
-  </si>
-  <si>
     <t>collector_number</t>
   </si>
   <si>
@@ -239,28 +443,34 @@
     <t>ability_kind_id</t>
   </si>
   <si>
+    <t>resolution_requirement_id</t>
+  </si>
+  <si>
+    <t>active_zone_id</t>
+  </si>
+  <si>
+    <t>implementation_mode</t>
+  </si>
+  <si>
     <t>trigger_id</t>
   </si>
   <si>
-    <t>resolution_requirement_id</t>
-  </si>
-  <si>
-    <t>active_zone_id</t>
-  </si>
-  <si>
-    <t>implementation_mode</t>
+    <t>module_key</t>
+  </si>
+  <si>
+    <t>parent_ability_id</t>
+  </si>
+  <si>
+    <t>condition_id</t>
   </si>
   <si>
     <t>event_type_id</t>
   </si>
   <si>
-    <t>module_key</t>
-  </si>
-  <si>
     <t>event_stage_id</t>
   </si>
   <si>
-    <t>parent_ability_id</t>
+    <t>parent_condition_id</t>
   </si>
   <si>
     <t>subject_reference_type_id</t>
@@ -269,42 +479,36 @@
     <t>player_reference_type_id</t>
   </si>
   <si>
+    <t>condition_kind_id</t>
+  </si>
+  <si>
     <t>phase_id</t>
   </si>
   <si>
+    <t>logical_operator_id</t>
+  </si>
+  <si>
     <t>from_zone_id</t>
   </si>
   <si>
+    <t>negated</t>
+  </si>
+  <si>
     <t>to_zone_id</t>
   </si>
   <si>
+    <t>left_expression_id</t>
+  </si>
+  <si>
     <t>filter_condition_id</t>
   </si>
   <si>
+    <t>comparison_operator_id</t>
+  </si>
+  <si>
     <t>timing_window_id</t>
   </si>
   <si>
-    <t>condition_id</t>
-  </si>
-  <si>
-    <t>parent_condition_id</t>
-  </si>
-  <si>
-    <t>condition_kind_id</t>
-  </si>
-  <si>
-    <t>logical_operator_id</t>
-  </si>
-  <si>
-    <t>negated</t>
-  </si>
-  <si>
-    <t>left_expression_id</t>
-  </si>
-  <si>
-    <t>comparison_operator_id</t>
-  </si>
-  <si>
     <t>right_expression_id</t>
   </si>
   <si>
@@ -356,16 +560,16 @@
     <t>source_reference_type_id</t>
   </si>
   <si>
+    <t>additional_cost</t>
+  </si>
+  <si>
+    <t>refundable</t>
+  </si>
+  <si>
     <t>effect_id</t>
   </si>
   <si>
-    <t>additional_cost</t>
-  </si>
-  <si>
     <t>parent_effect_id</t>
-  </si>
-  <si>
-    <t>refundable</t>
   </si>
   <si>
     <t>branch_key</t>
@@ -848,19 +1052,333 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="27.25"/>
+    <col customWidth="1" min="2" max="2" width="31.0"/>
+    <col customWidth="1" min="3" max="3" width="11.13"/>
+    <col customWidth="1" min="4" max="4" width="124.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -880,31 +1398,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -927,46 +1445,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>71</v>
+        <v>138</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>73</v>
+        <v>140</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -989,52 +1507,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1062,46 +1580,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>85</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>154</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>90</v>
+        <v>158</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1128,64 +1646,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>160</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>161</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>96</v>
+        <v>164</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>97</v>
+        <v>165</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1208,52 +1726,52 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1281,79 +1799,79 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="W1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1380,46 +1898,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1441,37 +1959,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1493,40 +2011,40 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>101</v>
+        <v>169</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1543,31 +2061,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1587,37 +2105,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>141</v>
+        <v>209</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>91</v>
+        <v>159</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1640,55 +2158,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>210</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1705,28 +2223,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>151</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>133</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1747,31 +2265,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>221</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>156</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1791,22 +2309,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1823,31 +2341,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1867,34 +2385,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1917,61 +2435,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>33</v>
+        <v>102</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>103</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>38</v>
+        <v>111</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>43</v>
+        <v>115</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1991,37 +2509,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2043,49 +2561,49 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>118</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -2105,34 +2623,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>61</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
